--- a/outputs/evaluation/architecture/validation/gemini-3-5/CF_M01/run_2/CF_M01_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/gemini-3-5/CF_M01/run_2/CF_M01_arch_eval.xlsx
@@ -508,6 +508,8 @@
         <v>0.9034</v>
       </c>
     </row>
+    <row r="5"/>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -590,7 +592,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>0.9643</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
